--- a/_to_delete/приложение по застройщику/Приложение 1 - Самолет.xlsx
+++ b/_to_delete/приложение по застройщику/Приложение 1 - Самолет.xlsx
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,6 +186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -536,22 +537,22 @@
     <col width="21.140625" customWidth="1" min="3" max="3"/>
     <col width="18.85546875" customWidth="1" min="4" max="4"/>
     <col width="16.7109375" customWidth="1" min="5" max="5"/>
-    <col width="22.85546875" customWidth="1" min="6" max="6"/>
-    <col width="22.85546875" customWidth="1" min="7" max="7"/>
-    <col width="21.5703125" customWidth="1" min="8" max="8"/>
-    <col width="29.42578125" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="22.85546875" customWidth="1" min="11" max="11"/>
-    <col width="26.140625" customWidth="1" min="12" max="12"/>
-    <col width="20.85546875" customWidth="1" min="13" max="13"/>
-    <col width="25.42578125" customWidth="1" min="14" max="14"/>
-    <col width="22.85546875" customWidth="1" min="15" max="15"/>
+    <col width="16.5703125" customWidth="1" min="6" max="6"/>
+    <col width="16.5703125" customWidth="1" min="7" max="7"/>
+    <col width="22.85546875" customWidth="1" min="8" max="8"/>
+    <col width="21.5703125" customWidth="1" min="9" max="9"/>
+    <col width="29.42578125" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="22.85546875" customWidth="1" min="12" max="12"/>
+    <col width="26.140625" customWidth="1" min="13" max="13"/>
+    <col width="20.85546875" customWidth="1" min="14" max="14"/>
+    <col width="25.42578125" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Приложение 2 Сроки передачи ключей</t>
+          <t>Приложение 1 Сроки передачи ключей</t>
         </is>
       </c>
     </row>
@@ -612,8 +613,12 @@
 с переносом срока, ед.</t>
         </is>
       </c>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="8" t="n"/>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>из них:</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="n"/>
       <c r="O3" s="8" t="n"/>
     </row>
     <row r="4" ht="32.25" customHeight="1">
@@ -621,14 +626,18 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="13" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="12" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Заключено ДС к ДДУ</t>
+        </is>
+      </c>
       <c r="N4" s="8" t="n"/>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -641,7 +650,7 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="F5" s="10" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
@@ -653,7 +662,11 @@
           <t>количество ДС к ДДУ, ед.</t>
         </is>
       </c>
-      <c r="N5" s="12" t="n"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>дата передачи согласно ДС</t>
+        </is>
+      </c>
       <c r="O5" s="7" t="n"/>
     </row>
     <row r="6">
@@ -2172,17 +2185,17 @@
   <mergeCells count="13">
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
-    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="L3:L5"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="D3:D5"/>
     <mergeCell ref="G3:G5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="J3:J5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="46" fitToHeight="0"/>
